--- a/excels/Research.xlsx
+++ b/excels/Research.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CED TD-11\Downloads\fmain\NITW-Transportation-Division-main\excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54995595-8062-4994-8CCE-8230C201FB3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Research_completed" sheetId="1" r:id="rId1"/>
-    <sheet name="Research_ongoing" sheetId="2" r:id="rId2"/>
+    <sheet name="Research_ongoing" sheetId="2" r:id="rId1"/>
+    <sheet name="Research_completed" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="127">
   <si>
     <t>S.No.</t>
   </si>
@@ -250,13 +251,169 @@
   </si>
   <si>
     <t>Study of pedestrian exposure to traffic emissions and corresponding travel behavior</t>
+  </si>
+  <si>
+    <t>Project_Title</t>
+  </si>
+  <si>
+    <t>Research_Domain</t>
+  </si>
+  <si>
+    <t>Technology_Used</t>
+  </si>
+  <si>
+    <t>Start_Date</t>
+  </si>
+  <si>
+    <t>Current_Status</t>
+  </si>
+  <si>
+    <t>Completion_Percentage</t>
+  </si>
+  <si>
+    <t>Team_Size</t>
+  </si>
+  <si>
+    <t>Funding_Amount_USD</t>
+  </si>
+  <si>
+    <t>AI-Based Crop Disease Detection</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>YOLOv8, CNN</t>
+  </si>
+  <si>
+    <t>2025-02-08</t>
+  </si>
+  <si>
+    <t>Data Collection</t>
+  </si>
+  <si>
+    <t>Smart Traffic Monitoring</t>
+  </si>
+  <si>
+    <t>Computer Vision</t>
+  </si>
+  <si>
+    <t>YOLOv8, DeepSORT</t>
+  </si>
+  <si>
+    <t>2025-06-27</t>
+  </si>
+  <si>
+    <t>Development</t>
+  </si>
+  <si>
+    <t>Blockchain Voting System</t>
+  </si>
+  <si>
+    <t>Cyber Security</t>
+  </si>
+  <si>
+    <t>Ethereum, Solidity</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>Deployment</t>
+  </si>
+  <si>
+    <t>IoT Smart Home Automation</t>
+  </si>
+  <si>
+    <t>Internet of Things</t>
+  </si>
+  <si>
+    <t>ESP32, MQTT</t>
+  </si>
+  <si>
+    <t>2025-09-03</t>
+  </si>
+  <si>
+    <t>Healthcare Chatbot</t>
+  </si>
+  <si>
+    <t>Natural Language Processing</t>
+  </si>
+  <si>
+    <t>Transformers, Python</t>
+  </si>
+  <si>
+    <t>2025-07-10</t>
+  </si>
+  <si>
+    <t>Autonomous Delivery Robot</t>
+  </si>
+  <si>
+    <t>Robotics</t>
+  </si>
+  <si>
+    <t>ROS, LiDAR</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>Planning</t>
+  </si>
+  <si>
+    <t>Fake News Detection</t>
+  </si>
+  <si>
+    <t>Machine Learning</t>
+  </si>
+  <si>
+    <t>BERT, NLP</t>
+  </si>
+  <si>
+    <t>2025-09-17</t>
+  </si>
+  <si>
+    <t>Renewable Energy Prediction</t>
+  </si>
+  <si>
+    <t>Data Science</t>
+  </si>
+  <si>
+    <t>LSTM, TensorFlow</t>
+  </si>
+  <si>
+    <t>2025-12-17</t>
+  </si>
+  <si>
+    <t>AR Interior Design App</t>
+  </si>
+  <si>
+    <t>Augmented Reality</t>
+  </si>
+  <si>
+    <t>Unity, ARCore</t>
+  </si>
+  <si>
+    <t>2025-03-29</t>
+  </si>
+  <si>
+    <t>Student Performance Analysis</t>
+  </si>
+  <si>
+    <t>Educational Analytics</t>
+  </si>
+  <si>
+    <t>Python, Pandas</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -271,6 +428,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -293,7 +455,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -301,6 +463,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -580,7 +744,313 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" s="3">
+        <v>94</v>
+      </c>
+      <c r="G2" s="3">
+        <v>3</v>
+      </c>
+      <c r="H2" s="3">
+        <v>12833</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F3" s="3">
+        <v>47</v>
+      </c>
+      <c r="G3" s="3">
+        <v>4</v>
+      </c>
+      <c r="H3" s="3">
+        <v>35013</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F4" s="3">
+        <v>92</v>
+      </c>
+      <c r="G4" s="3">
+        <v>7</v>
+      </c>
+      <c r="H4" s="3">
+        <v>34910</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F5" s="3">
+        <v>46</v>
+      </c>
+      <c r="G5" s="3">
+        <v>2</v>
+      </c>
+      <c r="H5" s="3">
+        <v>31756</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F6" s="3">
+        <v>92</v>
+      </c>
+      <c r="G6" s="3">
+        <v>4</v>
+      </c>
+      <c r="H6" s="3">
+        <v>5826</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F7" s="3">
+        <v>52</v>
+      </c>
+      <c r="G7" s="3">
+        <v>7</v>
+      </c>
+      <c r="H7" s="3">
+        <v>19428</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F8" s="3">
+        <v>21</v>
+      </c>
+      <c r="G8" s="3">
+        <v>2</v>
+      </c>
+      <c r="H8" s="3">
+        <v>32061</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F9" s="3">
+        <v>80</v>
+      </c>
+      <c r="G9" s="3">
+        <v>9</v>
+      </c>
+      <c r="H9" s="3">
+        <v>5932</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F10" s="3">
+        <v>31</v>
+      </c>
+      <c r="G10" s="3">
+        <v>6</v>
+      </c>
+      <c r="H10" s="3">
+        <v>27967</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F11" s="3">
+        <v>73</v>
+      </c>
+      <c r="G11" s="3">
+        <v>4</v>
+      </c>
+      <c r="H11" s="3">
+        <v>48599</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1103,13 +1573,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/excels/Research.xlsx
+++ b/excels/Research.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -433,6 +433,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -455,7 +456,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -463,7 +464,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -759,288 +759,288 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2">
         <v>94</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2">
         <v>3</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2">
         <v>12833</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>89</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>90</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" t="s">
         <v>91</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" t="s">
         <v>92</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3">
         <v>47</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3">
         <v>4</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3">
         <v>35013</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" t="s">
         <v>93</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4">
         <v>92</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4">
         <v>7</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4">
         <v>34910</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" t="s">
         <v>98</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" t="s">
         <v>101</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5">
         <v>46</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5">
         <v>2</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5">
         <v>31756</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" t="s">
         <v>102</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" t="s">
         <v>103</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" t="s">
         <v>105</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" t="s">
         <v>97</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6">
         <v>92</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6">
         <v>4</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6">
         <v>5826</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" t="s">
         <v>107</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" t="s">
         <v>108</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" t="s">
         <v>109</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" t="s">
         <v>110</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7">
         <v>52</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7">
         <v>7</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7">
         <v>19428</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" t="s">
         <v>111</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" t="s">
         <v>112</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" t="s">
         <v>113</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" t="s">
         <v>114</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" t="s">
         <v>97</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8">
         <v>21</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8">
         <v>2</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8">
         <v>32061</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" t="s">
         <v>115</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" t="s">
         <v>118</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" t="s">
         <v>92</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9">
         <v>80</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9">
         <v>9</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9">
         <v>5932</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" t="s">
         <v>119</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" t="s">
         <v>120</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" t="s">
         <v>121</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" t="s">
         <v>122</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" t="s">
         <v>110</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10">
         <v>31</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10">
         <v>6</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10">
         <v>27967</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" t="s">
         <v>123</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" t="s">
         <v>124</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" t="s">
         <v>125</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" t="s">
         <v>126</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" t="s">
         <v>97</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11">
         <v>73</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11">
         <v>4</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11">
         <v>48599</v>
       </c>
     </row>

--- a/excels/Research.xlsx
+++ b/excels/Research.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54995595-8062-4994-8CCE-8230C201FB3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D22B51BB-3B8D-4670-A29C-B6286DFC62B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="81">
   <si>
     <t>S.No.</t>
   </si>
@@ -256,157 +256,19 @@
     <t>Project_Title</t>
   </si>
   <si>
-    <t>Research_Domain</t>
-  </si>
-  <si>
-    <t>Technology_Used</t>
-  </si>
-  <si>
     <t>Start_Date</t>
   </si>
   <si>
-    <t>Current_Status</t>
-  </si>
-  <si>
-    <t>Completion_Percentage</t>
-  </si>
-  <si>
-    <t>Team_Size</t>
-  </si>
-  <si>
-    <t>Funding_Amount_USD</t>
-  </si>
-  <si>
-    <t>AI-Based Crop Disease Detection</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>YOLOv8, CNN</t>
-  </si>
-  <si>
-    <t>2025-02-08</t>
-  </si>
-  <si>
-    <t>Data Collection</t>
-  </si>
-  <si>
-    <t>Smart Traffic Monitoring</t>
-  </si>
-  <si>
-    <t>Computer Vision</t>
-  </si>
-  <si>
-    <t>YOLOv8, DeepSORT</t>
-  </si>
-  <si>
-    <t>2025-06-27</t>
-  </si>
-  <si>
-    <t>Development</t>
-  </si>
-  <si>
-    <t>Blockchain Voting System</t>
-  </si>
-  <si>
-    <t>Cyber Security</t>
-  </si>
-  <si>
-    <t>Ethereum, Solidity</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>Deployment</t>
-  </si>
-  <si>
-    <t>IoT Smart Home Automation</t>
-  </si>
-  <si>
-    <t>Internet of Things</t>
-  </si>
-  <si>
-    <t>ESP32, MQTT</t>
-  </si>
-  <si>
-    <t>2025-09-03</t>
-  </si>
-  <si>
-    <t>Healthcare Chatbot</t>
-  </si>
-  <si>
-    <t>Natural Language Processing</t>
-  </si>
-  <si>
-    <t>Transformers, Python</t>
-  </si>
-  <si>
-    <t>2025-07-10</t>
-  </si>
-  <si>
-    <t>Autonomous Delivery Robot</t>
-  </si>
-  <si>
-    <t>Robotics</t>
-  </si>
-  <si>
-    <t>ROS, LiDAR</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>Planning</t>
-  </si>
-  <si>
-    <t>Fake News Detection</t>
-  </si>
-  <si>
-    <t>Machine Learning</t>
-  </si>
-  <si>
-    <t>BERT, NLP</t>
-  </si>
-  <si>
-    <t>2025-09-17</t>
-  </si>
-  <si>
-    <t>Renewable Energy Prediction</t>
-  </si>
-  <si>
-    <t>Data Science</t>
-  </si>
-  <si>
-    <t>LSTM, TensorFlow</t>
-  </si>
-  <si>
-    <t>2025-12-17</t>
-  </si>
-  <si>
-    <t>AR Interior Design App</t>
-  </si>
-  <si>
-    <t>Augmented Reality</t>
-  </si>
-  <si>
-    <t>Unity, ARCore</t>
-  </si>
-  <si>
-    <t>2025-03-29</t>
-  </si>
-  <si>
-    <t>Student Performance Analysis</t>
-  </si>
-  <si>
-    <t>Educational Analytics</t>
-  </si>
-  <si>
-    <t>Python, Pandas</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
+    <t>Funding_amount</t>
+  </si>
+  <si>
+    <t>Funding_agency</t>
+  </si>
+  <si>
+    <t>PI&amp;CoPIs</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
 </sst>
 </file>
@@ -763,285 +625,189 @@
         <v>75</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>82</v>
-      </c>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F2">
-        <v>94</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>12833</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F3">
-        <v>47</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>35013</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F4">
-        <v>92</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
-      </c>
-      <c r="H4">
-        <v>34910</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>97</v>
-      </c>
-      <c r="F5">
-        <v>46</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>31756</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
-        <v>97</v>
-      </c>
-      <c r="F6">
-        <v>92</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>5826</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
-      </c>
-      <c r="F7">
-        <v>52</v>
-      </c>
-      <c r="G7">
-        <v>7</v>
-      </c>
-      <c r="H7">
-        <v>19428</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
-        <v>97</v>
-      </c>
-      <c r="F8">
-        <v>21</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-      <c r="H8">
-        <v>32061</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>92</v>
-      </c>
-      <c r="F9">
-        <v>80</v>
-      </c>
-      <c r="G9">
-        <v>9</v>
-      </c>
-      <c r="H9">
-        <v>5932</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>110</v>
-      </c>
-      <c r="F10">
-        <v>31</v>
-      </c>
-      <c r="G10">
-        <v>6</v>
-      </c>
-      <c r="H10">
-        <v>27967</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
-        <v>97</v>
-      </c>
-      <c r="F11">
-        <v>73</v>
-      </c>
-      <c r="G11">
-        <v>4</v>
-      </c>
-      <c r="H11">
-        <v>48599</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/excels/Research.xlsx
+++ b/excels/Research.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D22B51BB-3B8D-4670-A29C-B6286DFC62B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26898774-DFFC-4A3E-ADFE-8E680D801BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="90">
   <si>
     <t>S.No.</t>
   </si>
@@ -268,7 +268,34 @@
     <t>PI&amp;CoPIs</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>A study on Pedestrian Exposure to National Highways along the Built-up Areas: Towards Development of Pedestrian Crossing Treatments to lmprove Pedestrian Safety.</t>
+  </si>
+  <si>
+    <t>Rs. 45,03,000</t>
+  </si>
+  <si>
+    <t>National Highways Authority of India (Ministry of Road Transport and Highways, Government of lndia) (NHAI)</t>
+  </si>
+  <si>
+    <t>Prof. B Raghuram Kadali</t>
+  </si>
+  <si>
+    <t>Safe System perspective on vulnerable road users in India</t>
+  </si>
+  <si>
+    <t>Rs. 74,16,000</t>
+  </si>
+  <si>
+    <t>Scheme for Promotion of Academic &amp; Research Collaboration (SPARC)</t>
+  </si>
+  <si>
+    <t>Modelling and Simulation Techniques for Transport Network on National Highways and Urban Roads-under Center for Advanced Transportation Technology and Systems (CATTS)</t>
+  </si>
+  <si>
+    <t>Rs. 230, 90,000</t>
+  </si>
+  <si>
+    <t>Indian Academy of Highway Engineers (IAHE), MoRTH</t>
   </si>
 </sst>
 </file>
@@ -318,7 +345,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -327,6 +354,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -607,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.5703125" bestFit="1" customWidth="1"/>
@@ -645,173 +673,58 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2" t="s">
-        <v>80</v>
+        <v>82</v>
+      </c>
+      <c r="D2" s="4">
+        <v>45809</v>
       </c>
       <c r="E2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D3" t="s">
-        <v>80</v>
+        <v>86</v>
+      </c>
+      <c r="D3" s="4">
+        <v>45383</v>
       </c>
       <c r="E3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" t="s">
-        <v>80</v>
+        <v>89</v>
+      </c>
+      <c r="D4" s="4">
+        <v>45261</v>
       </c>
       <c r="E4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" t="s">
-        <v>80</v>
-      </c>
-      <c r="E8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D10" t="s">
-        <v>80</v>
-      </c>
-      <c r="E10" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D11" t="s">
-        <v>80</v>
-      </c>
-      <c r="E11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E4">
+    <sortCondition descending="1" ref="D2:D4"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/excels/Research.xlsx
+++ b/excels/Research.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26898774-DFFC-4A3E-ADFE-8E680D801BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069B4D0F-B904-4908-9E2F-F29D9A8370A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="92">
   <si>
     <t>S.No.</t>
   </si>
@@ -277,9 +277,6 @@
     <t>National Highways Authority of India (Ministry of Road Transport and Highways, Government of lndia) (NHAI)</t>
   </si>
   <si>
-    <t>Prof. B Raghuram Kadali</t>
-  </si>
-  <si>
     <t>Safe System perspective on vulnerable road users in India</t>
   </si>
   <si>
@@ -296,6 +293,15 @@
   </si>
   <si>
     <t>Indian Academy of Highway Engineers (IAHE), MoRTH</t>
+  </si>
+  <si>
+    <t>Prof. B Raghuram Kadali, Prof. C. S. R. K. Prasad, Prof. K. V. R. Ravi Shankar</t>
+  </si>
+  <si>
+    <t>Prof. K. V. R. Ravi Shankar, Prof. B Raghuram Kadali</t>
+  </si>
+  <si>
+    <t>Prof. B Raghuram Kadali, Prof. C. S. R. K. Prasad, Prof. K. V. R. Ravi Shankar, Prof. Arpan Mehar</t>
   </si>
 </sst>
 </file>
@@ -642,7 +648,7 @@
     <col min="2" max="2" width="26.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="67.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
@@ -682,41 +688,41 @@
         <v>45809</v>
       </c>
       <c r="E2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" t="s">
         <v>84</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>85</v>
-      </c>
-      <c r="C3" t="s">
-        <v>86</v>
       </c>
       <c r="D3" s="4">
         <v>45383</v>
       </c>
       <c r="E3" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" t="s">
         <v>87</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>88</v>
-      </c>
-      <c r="C4" t="s">
-        <v>89</v>
       </c>
       <c r="D4" s="4">
         <v>45261</v>
       </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/excels/Research.xlsx
+++ b/excels/Research.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069B4D0F-B904-4908-9E2F-F29D9A8370A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A6567A-61FF-4CEE-B788-B70E0569E844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -295,13 +295,13 @@
     <t>Indian Academy of Highway Engineers (IAHE), MoRTH</t>
   </si>
   <si>
-    <t>Prof. B Raghuram Kadali, Prof. C. S. R. K. Prasad, Prof. K. V. R. Ravi Shankar</t>
-  </si>
-  <si>
     <t>Prof. K. V. R. Ravi Shankar, Prof. B Raghuram Kadali</t>
   </si>
   <si>
-    <t>Prof. B Raghuram Kadali, Prof. C. S. R. K. Prasad, Prof. K. V. R. Ravi Shankar, Prof. Arpan Mehar</t>
+    <t>Prof. C. S. R. K. Prasad, Prof. B Raghuram Kadali, Prof. K. V. R. Ravi Shankar</t>
+  </si>
+  <si>
+    <t>Prof. C. S. R. K. Prasad, Prof. B Raghuram Kadali, Prof. K. V. R. Ravi Shankar, Prof. Arpan Mehar</t>
   </si>
 </sst>
 </file>
@@ -688,7 +688,7 @@
         <v>45809</v>
       </c>
       <c r="E2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -705,7 +705,7 @@
         <v>45383</v>
       </c>
       <c r="E3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">

--- a/excels/Research.xlsx
+++ b/excels/Research.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A6567A-61FF-4CEE-B788-B70E0569E844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAEF67B1-1910-45E0-8996-B1A8CF9CA0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Research_ongoing" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="123">
   <si>
     <t>S.No.</t>
   </si>
@@ -43,6 +43,30 @@
     <t>Amount (Rs. Lakhs)</t>
   </si>
   <si>
+    <t>Project_Title</t>
+  </si>
+  <si>
+    <t>Start_Date</t>
+  </si>
+  <si>
+    <t>In-situ Performance Evaluation of Low-Volume Rural Roads Constructed with Geosynthetics/Geotextiles</t>
+  </si>
+  <si>
+    <t>Safe System perspective on vulnerable road users in India</t>
+  </si>
+  <si>
+    <t>MoRTH</t>
+  </si>
+  <si>
+    <t>Evaluation of Traffic Emissions based on varied roadway characteristics</t>
+  </si>
+  <si>
+    <t>MHRD-NIT Warangal</t>
+  </si>
+  <si>
+    <t>Development of Trip Generation Manual for Indian Cities</t>
+  </si>
+  <si>
     <t>Permanent Traffic Counting Station</t>
   </si>
   <si>
@@ -214,9 +238,6 @@
     <t>SoAR-15: Development of Deterioration Models for Pavements and Bridges</t>
   </si>
   <si>
-    <t>MoRTH</t>
-  </si>
-  <si>
     <t>SoAR-14: Establishing Correlation between Various Distress Types and International Roughness Index (IRI) / Deflection for Roads and Bridges</t>
   </si>
   <si>
@@ -241,9 +262,6 @@
     <t>2021–24</t>
   </si>
   <si>
-    <t>Development of Trip Generation Manual for Indian Cities</t>
-  </si>
-  <si>
     <t>CSIR-CRRI</t>
   </si>
   <si>
@@ -253,18 +271,36 @@
     <t>Study of pedestrian exposure to traffic emissions and corresponding travel behavior</t>
   </si>
   <si>
-    <t>Project_Title</t>
-  </si>
-  <si>
-    <t>Start_Date</t>
+    <t>Development of Warrants for Full Depth Reclamation Projects</t>
+  </si>
+  <si>
+    <t>Laboratory Performance Evaluation of Cementitious Full Depth Reclamation Mixes</t>
+  </si>
+  <si>
+    <t>NRIDA, Ministry of Rural Development</t>
+  </si>
+  <si>
+    <t>Strength and Durability Assessment of Full Depth Reclamation Mixes</t>
+  </si>
+  <si>
+    <t>Vasu Enterprises, Kolkata</t>
+  </si>
+  <si>
+    <t>Development of Guidelines for Dense Graded Bituminous mix as Thin Surface Course Layer for Low Volume Roads</t>
+  </si>
+  <si>
+    <t>Performance evaluation of different surface course mixes in low volume roads</t>
+  </si>
+  <si>
+    <t>Evaluation of PAMA modified bituminous mixes</t>
+  </si>
+  <si>
+    <t>Funding_agency</t>
   </si>
   <si>
     <t>Funding_amount</t>
   </si>
   <si>
-    <t>Funding_agency</t>
-  </si>
-  <si>
     <t>PI&amp;CoPIs</t>
   </si>
   <si>
@@ -277,15 +313,6 @@
     <t>National Highways Authority of India (Ministry of Road Transport and Highways, Government of lndia) (NHAI)</t>
   </si>
   <si>
-    <t>Safe System perspective on vulnerable road users in India</t>
-  </si>
-  <si>
-    <t>Rs. 74,16,000</t>
-  </si>
-  <si>
-    <t>Scheme for Promotion of Academic &amp; Research Collaboration (SPARC)</t>
-  </si>
-  <si>
     <t>Modelling and Simulation Techniques for Transport Network on National Highways and Urban Roads-under Center for Advanced Transportation Technology and Systems (CATTS)</t>
   </si>
   <si>
@@ -295,20 +322,86 @@
     <t>Indian Academy of Highway Engineers (IAHE), MoRTH</t>
   </si>
   <si>
-    <t>Prof. K. V. R. Ravi Shankar, Prof. B Raghuram Kadali</t>
+    <t>2021 - 2022</t>
+  </si>
+  <si>
+    <t>SERB-SPARC</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NRIDA</t>
+  </si>
+  <si>
+    <t>2023 - 24</t>
+  </si>
+  <si>
+    <t>2024 - 26</t>
+  </si>
+  <si>
+    <t>2023 - 23</t>
+  </si>
+  <si>
+    <t>LSGD</t>
+  </si>
+  <si>
+    <t>2020 - 2023</t>
+  </si>
+  <si>
+    <t>Raeun Mercentile Pvt Ltd</t>
+  </si>
+  <si>
+    <t>Effect of Flooding on Flexible Pavement Performance and Formulation of Treatment Strategies for Sustaining Resilience in Road Infrastructure</t>
+  </si>
+  <si>
+    <t>Rs. 45.32</t>
+  </si>
+  <si>
+    <t>Department of Science and Technology, Science and Engineering</t>
+  </si>
+  <si>
+    <t>Prof. S Shankar</t>
+  </si>
+  <si>
+    <t>Performance Evaluation of Full-Depth Reclamation(FDR) Roads in the State of Uttar Pradesh</t>
+  </si>
+  <si>
+    <t>NRIDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2024 -26</t>
+  </si>
+  <si>
+    <t>2023 - 25</t>
+  </si>
+  <si>
+    <t>Rs. 71,16,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPARC </t>
+  </si>
+  <si>
+    <t>Evaluation of Interfacial Bond Strength in Bituminous Pavement Layer and Analysis Using BISAR 3 Software Tool</t>
+  </si>
+  <si>
+    <t>2022 - 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023 - 24 </t>
   </si>
   <si>
     <t>Prof. C. S. R. K. Prasad, Prof. B Raghuram Kadali, Prof. K. V. R. Ravi Shankar</t>
   </si>
   <si>
     <t>Prof. C. S. R. K. Prasad, Prof. B Raghuram Kadali, Prof. K. V. R. Ravi Shankar, Prof. Arpan Mehar</t>
+  </si>
+  <si>
+    <t>Prof. K. V. R. Ravi Shankar,  Prof. B Raghuram Kadali</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -327,7 +420,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF212529"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -351,16 +463,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -640,8 +767,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.5703125" bestFit="1" customWidth="1"/>
@@ -655,604 +782,853 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
+      <c r="A1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D2" s="4">
+        <v>94</v>
+      </c>
+      <c r="D2" s="9">
         <v>45809</v>
       </c>
       <c r="E2" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D3" s="4">
-        <v>45383</v>
+        <v>97</v>
+      </c>
+      <c r="D3" s="9">
+        <v>45261</v>
       </c>
       <c r="E3" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D4" s="4">
-        <v>45261</v>
+        <v>109</v>
+      </c>
+      <c r="D4" s="9">
+        <v>45323</v>
       </c>
       <c r="E4" t="s">
-        <v>91</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D5" s="9">
+        <v>45383</v>
+      </c>
+      <c r="E5" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E4">
-    <sortCondition descending="1" ref="D2:D4"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="30.85546875" customWidth="1"/>
-    <col min="4" max="4" width="30.7109375" customWidth="1"/>
-    <col min="5" max="5" width="32.5703125" customWidth="1"/>
+    <col min="2" max="2" width="52.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="27.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="30.85546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="30.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="32.5703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="52.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="6">
+        <v>1</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0.26</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0.45</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="6">
+        <v>5</v>
+      </c>
+      <c r="F6"/>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="B7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="E2" s="2">
+      <c r="B8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="F8"/>
+      <c r="G8" s="5"/>
+    </row>
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="5"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="B10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
         <v>10</v>
       </c>
-      <c r="E3" s="2">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="B11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="B12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="6">
+        <v>35</v>
+      </c>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
         <v>12</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="B13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="6">
+        <v>10</v>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+    </row>
+    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
         <v>13</v>
       </c>
-      <c r="E4" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="B14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="6">
+        <v>16.5</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
         <v>14</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="B15" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="6">
+        <v>4.5</v>
+      </c>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="6">
+        <v>5</v>
+      </c>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="6">
+        <v>20</v>
+      </c>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" s="6">
+        <v>7</v>
+      </c>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="6">
+        <v>19.5</v>
+      </c>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E21" s="6">
+        <v>132.5</v>
+      </c>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+    </row>
+    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>21</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E22" s="6">
+        <v>20.9</v>
+      </c>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>22</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E23" s="6">
+        <v>21.72</v>
+      </c>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>23</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="10">
+        <v>2017</v>
+      </c>
+      <c r="E24" s="6">
+        <v>8.2799999999999994</v>
+      </c>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="10">
+        <v>2017</v>
+      </c>
+      <c r="E25" s="6">
+        <v>6.28</v>
+      </c>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+    </row>
+    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <v>25</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E26" s="6">
+        <v>30.49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <v>26</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="10">
+        <v>2019</v>
+      </c>
+      <c r="E27" s="6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>27</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="E28" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <v>28</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>29</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>30</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E31" s="6">
+        <v>44.17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>31</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="C32" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E32" s="6">
+        <v>8.14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>32</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E33" s="6">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>33</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="E34" s="6">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>34</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E35" s="6">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>35</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E36" s="6">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <v>36</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E37" s="6">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="E38" s="6">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="E39" s="6">
         <v>15</v>
       </c>
-      <c r="E5" s="2">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="2">
-        <v>16.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="C40" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
         <v>40</v>
       </c>
-      <c r="E15" s="2">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="2">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E20" s="2">
-        <v>19.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E21" s="2">
-        <v>132.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E22" s="2">
-        <v>20.9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E23" s="2">
-        <v>21.72</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="2">
-        <v>2017</v>
-      </c>
-      <c r="E24" s="2">
-        <v>8.2799999999999994</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="2">
-        <v>2017</v>
-      </c>
-      <c r="E25" s="2">
-        <v>6.28</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" s="2">
-        <v>30.49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27" s="2">
-        <v>2019</v>
-      </c>
-      <c r="E27" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E28" s="2">
-        <v>44.17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
-        <v>28</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E29" s="2">
-        <v>8.14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E30" s="2">
-        <v>28.5</v>
+      <c r="B41" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E41" s="2">
+        <v>45.76</v>
       </c>
     </row>
   </sheetData>
